--- a/실습파일/실습2_마크다운정리와_분할기록.xlsx
+++ b/실습파일/실습2_마크다운정리와_분할기록.xlsx
@@ -584,7 +584,7 @@
     <row r="3">
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>걸리는 시간: 약 9분   ★ 40분 핵심 코스   |   [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [일반 기능]</t>
+          <t>걸리는 시간: 약 9분   ★ 40분 핵심 코스   |   [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [일반 기능]</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [일반 기능] → [마크다운 문법 기호, 빈 줄 정리]</t>
+          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [일반 기능] → [마크다운 문법 기호, 빈 줄 정리]</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
     <row r="21" ht="22" customHeight="1">
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>1.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [일반 기능] → [셀 내용 행 단위 분할 기록기]</t>
+          <t>1.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [일반 기능] → [셀 내용 행 단위 분할 기록기]</t>
         </is>
       </c>
     </row>
